--- a/backend/menada_design.xlsx
+++ b/backend/menada_design.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>singlenet</t>
+          <t>radionet</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,17 +528,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Host</t>
+          <t>Host and Base</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00035-001760</t>
+          <t>74360-007600</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singlenet Host</t>
+          <t>RadioNet HOST + BASE</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -553,96 +553,216 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74340-014900</t>
+          <t>74330-012195</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SingleNet RTU 2x2</t>
+          <t>RadioNet RTU 2DI-2DO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RTU 4x4</t>
+          <t>RTU Expandable</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>74340-015000</t>
+          <t>74330-012200</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SingleNet RTU 4x4</t>
+          <t>RadioNet RTU 2DI-1DO Expandable</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLSM</t>
+          <t>RADIONET SOLAR PANEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00035-008300</t>
+          <t>74330-005760</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SINGLENET SLSM LINE SUPPRESSION MODULE</t>
+          <t>RADIONET SOLAR PANEL KIT 9V-3W</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RTU 4x4+PLSM</t>
+          <t>Expans. Board</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>74340-015500</t>
+          <t>74330-013140</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SINGLENET RTU 4 LATCH OUT &amp;4 D.IN+PLSM</t>
+          <t>RadioNet Expansion Board 2DI-2DO</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RTU 2x2+PLSM</t>
+          <t>R-NET MONOPOL.ANT. 6M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74340-015400</t>
+          <t>74330-005060</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SINGLENET RTU 2 LATCH OUT&amp;2 D.IN+PLSM</t>
+          <t>R-NET MONOPOL.ANT.430-470 6M GROUNDED485</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ground Kit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>77100-005880</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ground Kit</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rnet battery</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>74330-003025</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>R-NET BATTERY 6V 1.3AH SLA NP1.2-6</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Serial Expansion card</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>00035-013150</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serial Expansion card, RS232/485/SDI12 </t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NETACAP 3.5V REGULATOR CARD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>74330-000006</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NETACAP 3.5V REGULATOR CARD #297 FOR DFM  </t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R-NET DCP CAPACITOR CARD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>74330-012240</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R-NET DCP CAPACITOR CARD</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NETACAP 6/60CM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>74730-000009</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SOIL MOISTURE NETACAP WP 6/60CM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/backend/menada_design.xlsx
+++ b/backend/menada_design.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
